--- a/iFST/messages.xlsx
+++ b/iFST/messages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github_repos/iFST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA4E9D2-8950-47D5-BC1F-5F2F59FBCE7A}"/>
+  <xr:revisionPtr revIDLastSave="488" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4500BDBA-379D-4778-AADB-7FE95CC2721D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="166">
   <si>
     <t>EN</t>
   </si>
@@ -554,6 +554,124 @@
   </si>
   <si>
     <t>segundos</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Willkommen zur Aufgabe!</t>
+  </si>
+  <si>
+    <t>Richtig</t>
+  </si>
+  <si>
+    <t>Falsch</t>
+  </si>
+  <si>
+    <t>Zeit</t>
+  </si>
+  <si>
+    <t>Sekunden</t>
+  </si>
+  <si>
+    <t>von</t>
+  </si>
+  <si>
+    <t>Ende des Blocks</t>
+  </si>
+  <si>
+    <t>Zur Aufgabe fortfahren</t>
+  </si>
+  <si>
+    <t>Welche Hand ist Ihre bevorzugte oder dominante Hand?</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Rechts</t>
+  </si>
+  <si>
+    <t>Sequenz korrekt!</t>
+  </si>
+  <si>
+    <t>Sequenz inkorrekt. Bitte geben Sie die Sequenz korrekt ein. Der Durchgang wird wiederholt.</t>
+  </si>
+  <si>
+    <t>Tasten korrekt!</t>
+  </si>
+  <si>
+    <t>Tasten inkorrekt. Sie müssen mit derselben Taste beginnen und enden. Der Durchgang wird wiederholt.</t>
+  </si>
+  <si>
+    <t>Durchgang abgeschlossen</t>
+  </si>
+  <si>
+    <t>Korrekte Durchgänge:</t>
+  </si>
+  <si>
+    <t>Visuelle Modalität</t>
+  </si>
+  <si>
+    <t>Kinästhetische Modalität</t>
+  </si>
+  <si>
+    <t>Beide Modalitäten</t>
+  </si>
+  <si>
+    <t>Weiter</t>
+  </si>
+  <si>
+    <t>Vorgestellte Fingersequenzaufgabe
+(iFST)</t>
+  </si>
+  <si>
+    <t>Leertaste drücken, um fortzufahren</t>
+  </si>
+  <si>
+    <t>Sie haben das Experiment abgeschlossen.
+Vielen Dank für Ihre Teilnahme!
+Das Experiment wird in 3 Sekunden beendet.</t>
+  </si>
+  <si>
+    <t>Sie beginnen nun mit dem Übungsteil.
+Ziel ist es, die Sequenzen korrekt einzugeben und sich mit dem Unterschied zwischen Ausführung und Vorstellung vertraut zu machen.
+In dieser Phase ist es entscheidend, dass Sie wie angegeben korrekt reagieren.</t>
+  </si>
+  <si>
+    <t>Sie gelangen erst dann zum nächsten Teil, wenn Sie alle Sequenzen sowohl in der Ausführung als auch in der Vorstellung korrekt beantwortet haben.
+Nachdem Sie nun geübt haben, beginnen Sie mit der eigentlichen Aufgabe.
+Denken Sie daran: Ihre ERSTE PRIORITÄT ist es, GENAU zu antworten.
+Ihre ZWEITE PRIORITÄT ist es, die Sequenz so SCHNELL WIE MÖGLICH abzuschließen.
+In diesem Teil erhalten Sie kein Feedback zu Ihrer Leistung, aber Sie erkennen das Ende eines Durchgangs daran, dass sich der Bildschirm ändert.</t>
+  </si>
+  <si>
+    <t>Sie haben die Hälfte der Aufgabe erreicht.
+Bitte machen Sie eine Pause von mindestens 1 Minute.
+Die Aufgabe wird nach ein paar Minuten automatisch fortgesetzt.</t>
+  </si>
+  <si>
+    <t>Sie haben den Block beendet.
+Nehmen Sie sich einen Moment Zeit für eine Pause, bevor Sie fortfahren.
+Die Aufgabe wird nach 1 Minute automatisch fortgesetzt.
+Sie können auch früher fortfahren, wenn Sie möchten. Warten Sie auf eine unten erscheinende Meldung.</t>
+  </si>
+  <si>
+    <t>Im nächsten Durchgang müssen Sie die Bewegung PHYSISCH AUSFÜHREN.
+Denken Sie daran, ALLE Tasten zu drücken.</t>
+  </si>
+  <si>
+    <t>Im nächsten Durchgang müssen Sie sich die Bewegung VORSTELLEN.
+Bitte konzentrieren Sie sich sowohl auf das SEHEN als auch auf das FÜHLEN der Bewegung.
+Denken Sie daran, dass Sie nur die ERSTE und LETZTE Taste drücken müssen.</t>
+  </si>
+  <si>
+    <t>Diese Sequenz PHYSISCH AUSFÜHREN
+(alle Tasten drücken).</t>
+  </si>
+  <si>
+    <t>Diese Sequenz VORSTELLEN
+(nur die erste/letzte Taste drücken).</t>
   </si>
 </sst>
 </file>
@@ -657,10 +775,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -960,13 +1074,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -979,8 +1093,11 @@
       <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -993,8 +1110,11 @@
       <c r="D2" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E2" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1007,8 +1127,11 @@
       <c r="D3" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1144,11 @@
       <c r="D4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1035,8 +1161,11 @@
       <c r="D5" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1049,8 +1178,11 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1063,8 +1195,11 @@
       <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -1077,8 +1212,11 @@
       <c r="D8" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -1091,8 +1229,11 @@
       <c r="D9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1105,8 +1246,11 @@
       <c r="D10" s="4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1119,8 +1263,11 @@
       <c r="D11" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1133,8 +1280,11 @@
       <c r="D12" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1147,8 +1297,11 @@
       <c r="D13" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1161,8 +1314,11 @@
       <c r="D14" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -1175,8 +1331,11 @@
       <c r="D15" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1189,8 +1348,11 @@
       <c r="D16" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1203,8 +1365,11 @@
       <c r="D17" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1217,8 +1382,11 @@
       <c r="D18" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1231,8 +1399,11 @@
       <c r="D19" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -1245,8 +1416,11 @@
       <c r="D20" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1259,8 +1433,11 @@
       <c r="D21" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1273,8 +1450,11 @@
       <c r="D22" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1287,8 +1467,11 @@
       <c r="D23" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1301,8 +1484,11 @@
       <c r="D24" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1315,8 +1501,11 @@
       <c r="D25" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -1329,8 +1518,11 @@
       <c r="D26" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -1343,8 +1535,11 @@
       <c r="D27" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -1357,8 +1552,11 @@
       <c r="D28" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1371,8 +1569,11 @@
       <c r="D29" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E29" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1385,8 +1586,11 @@
       <c r="D30" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E30" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1399,8 +1603,11 @@
       <c r="D31" s="5" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E31" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -1413,8 +1620,11 @@
       <c r="D32" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -1427,8 +1637,11 @@
       <c r="D33" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E33" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -1440,6 +1653,9 @@
       </c>
       <c r="D34" s="5" t="s">
         <v>103</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1464,6 +1680,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -1577,12 +1799,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
@@ -1592,6 +1808,21 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1605,19 +1836,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>